--- a/excelCfg/roguelike.xlsx
+++ b/excelCfg/roguelike.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R4bd77ee92acb4929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="R8e5868d4cee441a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="R14b8b98f1c7d4fe0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="Rac866eea1d744714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R03a584b1fc964844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="Rcdbd41f2f7ba42c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="R12bb550523c9412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="Rd781de9c7ca343f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1956,7 +1956,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4607fd436f44067"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd238ff21aadb4dc8"/>
 </x:worksheet>
 </file>
 
@@ -2905,7 +2905,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33347d37fd544ae7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca49798d11a14885"/>
 </x:worksheet>
 </file>
 
@@ -3895,7 +3895,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1356c4350aa84da2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67929c68f0b4012"/>
 </x:worksheet>
 </file>
 
@@ -4110,10 +4110,70 @@
         <x:v>183</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>attack_speed_percent</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>战斗属性</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>攻击速度</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>derived_attack_speed_percent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>basic_attack_bonus_percent</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>战斗属性</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>普攻加成</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>derived_basic_attack_bonus_percent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>health_amplification_percent</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>战斗属性</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>生命增幅</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>derived_health_amplification_percent</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8dc4312c1c24d53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b5b110a04147fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/excelCfg/roguelike.xlsx
+++ b/excelCfg/roguelike.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R8592e3de66254758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="Rff7cc0adfefe49b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="Rfa351a1797214123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R7b27e4a2f5bd4db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R5a2d7f8054704ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="Rf7e87046a22f421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="R094e7bf0c5af495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R1859d50fc4b94af0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2030,7 +2030,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737fd9c0719a4e02"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R856b91a33fb146ae"/>
 </x:worksheet>
 </file>
 
@@ -3358,6 +3358,398 @@
       <x:c r="P27"/>
       <x:c r="Q27"/>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>R_H_Q_TARGET</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>长虹贯日</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>贯日箭的穿透上限增加 {value}。</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>ui\selectHero\skills\a0n1.blp</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>target_count_add</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N28" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>R_H_Q_DAMAGE</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>裂云</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>贯日箭伤害增加 {value}%。</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>ui\selectHero\skills\a0n1.blp</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>damage_percent_add</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L29" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N29" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P29"/>
+      <x:c r="Q29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>R_H_W_PROJECTILE</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>七曜连珠</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>连珠追日额外射出 {value} 支箭。</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>ui\selectHero\skills\a0n2.blp</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>projectile_count_add</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N30" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P30"/>
+      <x:c r="Q30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>R_H_W_BOUNCE</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>追星折返</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>连珠追日的每支箭额外弹射 {value} 个敌人。</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>ui\selectHero\skills\a0n2.blp</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>bounce_count_add</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N31" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P31"/>
+      <x:c r="Q31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>R_H_E_PROC_DAMAGE</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>烈阳焚身</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>日痕爆发伤害增加 {value}%。</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>ui\selectHero\skills\a0n3.blp</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>proc_damage_percent_add</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K32" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L32" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N32" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P32"/>
+      <x:c r="Q32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>R_H_E_AREA</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>余烬燎原</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>日痕爆发范围增加 {value}。</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>ui\selectHero\skills\a0n3.blp</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>area_add</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J33" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K33" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L33" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N33" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>R_H_R_PROJECTILE</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>天弓再张</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>九曜坠落额外追加 {value} 支普通日箭。</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>ui\selectHero\skills\a0n4.blp</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>projectile_count_add</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P34"/>
+      <x:c r="Q34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>R_H_R_FINAL_DAMAGE</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>坠日余威</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>九曜坠落第九箭伤害增加 {value}%。</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>ui\selectHero\skills\a0n4.blp</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>final_damage_percent_add</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>add</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K35" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L35" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N35" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="B4:B19">
@@ -3371,7 +3763,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bb59f5a6a3b4cdb"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0fdd39d276640d1"/>
 </x:worksheet>
 </file>
 
@@ -3935,161 +4327,79 @@
       <x:c r="I24" s="27"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="31" t="str">
-        <x:v>NEZHA_A0N1_DAMAGE_ATTRIBUTE</x:v>
-      </x:c>
-      <x:c r="B25" s="31" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C25" s="31" t="str">
-        <x:v>A0N1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="str">
-        <x:v>damageAttribute</x:v>
-      </x:c>
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
       <x:c r="E25" s="36"/>
       <x:c r="F25" s="36"/>
       <x:c r="G25" s="36"/>
       <x:c r="H25" s="36"/>
-      <x:c r="I25" s="31" t="str">
-        <x:v>intelligence</x:v>
-      </x:c>
+      <x:c r="I25" s="31"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="27" t="str">
-        <x:v>NEZHA_A0N1_DAMAGE_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="B26" s="27" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="str">
-        <x:v>A0N1</x:v>
-      </x:c>
-      <x:c r="D26" s="27" t="str">
-        <x:v>damageMultiplierTenth</x:v>
-      </x:c>
+      <x:c r="A26" s="27"/>
+      <x:c r="B26" s="27"/>
+      <x:c r="C26" s="27"/>
+      <x:c r="D26" s="27"/>
       <x:c r="E26" s="35"/>
-      <x:c r="F26" s="35" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G26" s="35" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H26" s="35" t="n">
-        <x:v>18</x:v>
-      </x:c>
+      <x:c r="F26" s="35"/>
+      <x:c r="G26" s="35"/>
+      <x:c r="H26" s="35"/>
       <x:c r="I26" s="27"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="31" t="str">
-        <x:v>NEZHA_A0N2_DAMAGE_ATTRIBUTE</x:v>
-      </x:c>
-      <x:c r="B27" s="31" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C27" s="31" t="str">
-        <x:v>A0N2</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="str">
-        <x:v>damageAttribute</x:v>
-      </x:c>
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
       <x:c r="E27" s="36"/>
       <x:c r="F27" s="36"/>
       <x:c r="G27" s="36"/>
       <x:c r="H27" s="36"/>
-      <x:c r="I27" s="31" t="str">
-        <x:v>intelligence</x:v>
-      </x:c>
+      <x:c r="I27" s="31"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="27" t="str">
-        <x:v>NEZHA_A0N2_DAMAGE_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="B28" s="27" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="str">
-        <x:v>A0N2</x:v>
-      </x:c>
-      <x:c r="D28" s="27" t="str">
-        <x:v>damageMultiplierTenth</x:v>
-      </x:c>
+      <x:c r="A28" s="27"/>
+      <x:c r="B28" s="27"/>
+      <x:c r="C28" s="27"/>
+      <x:c r="D28" s="27"/>
       <x:c r="E28" s="35"/>
-      <x:c r="F28" s="35" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G28" s="35" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H28" s="35" t="n">
-        <x:v>18</x:v>
-      </x:c>
+      <x:c r="F28" s="35"/>
+      <x:c r="G28" s="35"/>
+      <x:c r="H28" s="35"/>
       <x:c r="I28" s="27"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="31" t="str">
-        <x:v>NEZHA_A0N4_PROC_DAMAGE_ATTRIBUTE</x:v>
-      </x:c>
-      <x:c r="B29" s="31" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C29" s="31" t="str">
-        <x:v>A0N4</x:v>
-      </x:c>
-      <x:c r="D29" s="31" t="str">
-        <x:v>procDamageAttribute</x:v>
-      </x:c>
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
       <x:c r="E29" s="36"/>
       <x:c r="F29" s="36"/>
       <x:c r="G29" s="36"/>
       <x:c r="H29" s="36"/>
-      <x:c r="I29" s="31" t="str">
-        <x:v>intelligence</x:v>
-      </x:c>
+      <x:c r="I29" s="31"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="27" t="str">
-        <x:v>NEZHA_A0N4_PROC_DAMAGE_MULTIPLIER</x:v>
-      </x:c>
-      <x:c r="B30" s="27" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="str">
-        <x:v>A0N4</x:v>
-      </x:c>
-      <x:c r="D30" s="27" t="str">
-        <x:v>procDamageMultiplierTenth</x:v>
-      </x:c>
+      <x:c r="A30" s="27"/>
+      <x:c r="B30" s="27"/>
+      <x:c r="C30" s="27"/>
+      <x:c r="D30" s="27"/>
       <x:c r="E30" s="35"/>
-      <x:c r="F30" s="35" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G30" s="35" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="F30" s="35"/>
+      <x:c r="G30" s="35"/>
       <x:c r="H30" s="35"/>
       <x:c r="I30" s="27"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="31" t="str">
-        <x:v>NEZHA_A0N4_PROC_CHANCE</x:v>
-      </x:c>
-      <x:c r="B31" s="31" t="str">
-        <x:v>H0N0</x:v>
-      </x:c>
-      <x:c r="C31" s="31" t="str">
-        <x:v>A0N4</x:v>
-      </x:c>
-      <x:c r="D31" s="31" t="str">
-        <x:v>procChance</x:v>
-      </x:c>
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
       <x:c r="E31" s="36"/>
-      <x:c r="F31" s="36" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G31" s="36" t="n">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="F31" s="36"/>
+      <x:c r="G31" s="36"/>
       <x:c r="H31" s="36"/>
       <x:c r="I31" s="31"/>
     </x:row>
@@ -4774,9 +5084,659 @@
       <x:c r="H62"/>
       <x:c r="I62"/>
     </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>HOUYI_Q_DAMAGE_ATTRIBUTE</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
+        <x:v>damageAttribute</x:v>
+      </x:c>
+      <x:c r="E63"/>
+      <x:c r="F63"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>HOUYI_Q_DAMAGE_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
+        <x:v>damageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E64"/>
+      <x:c r="F64" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H64" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>HOUYI_Q_RANGE</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E65" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F65"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>HOUYI_Q_WIDTH</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>width</x:v>
+      </x:c>
+      <x:c r="E66" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F66"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>HOUYI_Q_TARGET_COUNT</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>A0N1</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>targetCount</x:v>
+      </x:c>
+      <x:c r="E67" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F67"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>HOUYI_W_DAMAGE_ATTRIBUTE</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>damageAttribute</x:v>
+      </x:c>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>HOUYI_W_DAMAGE_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>damageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E69"/>
+      <x:c r="F69" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G69" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H69" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>HOUYI_W_RANGE</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>range</x:v>
+      </x:c>
+      <x:c r="E70" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="F70"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>HOUYI_W_PROJECTILE_COUNT</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>projectileCount</x:v>
+      </x:c>
+      <x:c r="E71" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F71"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>HOUYI_W_PROJECTILE_INTERVAL</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>projectileIntervalHundredths</x:v>
+      </x:c>
+      <x:c r="E72" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F72"/>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>HOUYI_W_BOUNCE_RANGE</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>bounceRange</x:v>
+      </x:c>
+      <x:c r="E73" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F73"/>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>HOUYI_W_BOUNCE_COUNT</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>A0N2</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>bounceCount</x:v>
+      </x:c>
+      <x:c r="E74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F74"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>HOUYI_E_PROC_DAMAGE_ATTRIBUTE</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>procDamageAttribute</x:v>
+      </x:c>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>HOUYI_E_PROC_DAMAGE_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>procDamageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E76"/>
+      <x:c r="F76" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G76" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H76" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>HOUYI_E_MAX_STACKS</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>maxStacks</x:v>
+      </x:c>
+      <x:c r="E77" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>HOUYI_E_DURATION</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>duration</x:v>
+      </x:c>
+      <x:c r="E78" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>HOUYI_E_PROC_AREA</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>procArea</x:v>
+      </x:c>
+      <x:c r="E79" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>HOUYI_E_SLOW_PERCENT</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>slowPercent</x:v>
+      </x:c>
+      <x:c r="E80" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>HOUYI_E_SLOW_DURATION</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>slowDurationHundredths</x:v>
+      </x:c>
+      <x:c r="E81" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>HOUYI_E_BOW_DAMAGE</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>itemProcDamagePercent</x:v>
+      </x:c>
+      <x:c r="E82" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>HOUYI_E_BOW_AREA</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>A0N3</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>itemProcAreaAdd</x:v>
+      </x:c>
+      <x:c r="E83" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="F83"/>
+      <x:c r="G83"/>
+      <x:c r="H83"/>
+      <x:c r="I83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>HOUYI_R_DAMAGE_ATTRIBUTE</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>damageAttribute</x:v>
+      </x:c>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>HOUYI_R_DAMAGE_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>damageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E85"/>
+      <x:c r="F85" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H85" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>HOUYI_R_FINAL_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>finalDamageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E86"/>
+      <x:c r="F86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H86" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>HOUYI_R_AREA</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>area</x:v>
+      </x:c>
+      <x:c r="E87" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>HOUYI_R_OUTER_RADIUS</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>outerRadius</x:v>
+      </x:c>
+      <x:c r="E88" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="F88"/>
+      <x:c r="G88"/>
+      <x:c r="H88"/>
+      <x:c r="I88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>HOUYI_R_PROJECTILE_COUNT</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>projectileCount</x:v>
+      </x:c>
+      <x:c r="E89" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>HOUYI_R_NORMAL_AREA</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>normalArea</x:v>
+      </x:c>
+      <x:c r="E90" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>HOUYI_R_FINAL_AREA</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>finalArea</x:v>
+      </x:c>
+      <x:c r="E91" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>HOUYI_R_DURATION</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>H0N0</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>A0N4</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>durationHundredths</x:v>
+      </x:c>
+      <x:c r="E92" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5e214c2c28b4dc5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6dc16630ebf47ab"/>
 </x:worksheet>
 </file>
 
@@ -5054,7 +6014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ed7eecd5e2545a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63bee14851046bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/excelCfg/roguelike.xlsx
+++ b/excelCfg/roguelike.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R5a2d7f8054704ce3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="Rf7e87046a22f421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="R094e7bf0c5af495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R1859d50fc4b94af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R986484eff25b4f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="R8b49c1bf6f874a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="Rc6ccb3f1c17b4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R946b5fed626240ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2030,7 +2030,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R856b91a33fb146ae"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f70bdf567e24619"/>
 </x:worksheet>
 </file>
 
@@ -3372,16 +3372,16 @@
         <x:v>A0N1</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>长虹贯日</x:v>
+        <x:v>分光箭</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>贯日箭的穿透上限增加 {value}。</x:v>
+        <x:v>贯日箭每级额外射出 {value} 支箭，方向依次为 +30°、−30°、+60°。</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>ui\selectHero\skills\a0n1.blp</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>target_count_add</x:v>
+        <x:v>projectile_count_add</x:v>
       </x:c>
       <x:c r="I28" t="str">
         <x:v>add</x:v>
@@ -3421,31 +3421,31 @@
         <x:v>A0N1</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>裂云</x:v>
+        <x:v>余晖复射</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>贯日箭伤害增加 {value}%。</x:v>
+        <x:v>贯日箭额外复射 {value} 轮，复射不额外消耗魔法。</x:v>
       </x:c>
       <x:c r="G29" t="str">
         <x:v>ui\selectHero\skills\a0n1.blp</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>damage_percent_add</x:v>
+        <x:v>repeat_count_add</x:v>
       </x:c>
       <x:c r="I29" t="str">
         <x:v>add</x:v>
       </x:c>
       <x:c r="J29" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K29" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L29" t="n">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M29" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N29" t="n">
         <x:v>100</x:v>
@@ -3763,7 +3763,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0fdd39d276640d1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ccc3818574445f"/>
 </x:worksheet>
 </file>
 
@@ -5153,7 +5153,7 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>HOUYI_Q_WIDTH</x:v>
+        <x:v>HOUYI_A0N1_DAMAGE_RADIUS</x:v>
       </x:c>
       <x:c r="B66" t="str">
         <x:v>H0N0</x:v>
@@ -5162,10 +5162,10 @@
         <x:v>A0N1</x:v>
       </x:c>
       <x:c r="D66" t="str">
-        <x:v>width</x:v>
+        <x:v>damageRadius</x:v>
       </x:c>
       <x:c r="E66" t="n">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F66"/>
       <x:c r="G66"/>
@@ -5174,7 +5174,7 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>HOUYI_Q_TARGET_COUNT</x:v>
+        <x:v>HOUYI_A0N1_PROJECTILE_SPEED</x:v>
       </x:c>
       <x:c r="B67" t="str">
         <x:v>H0N0</x:v>
@@ -5183,10 +5183,10 @@
         <x:v>A0N1</x:v>
       </x:c>
       <x:c r="D67" t="str">
-        <x:v>targetCount</x:v>
+        <x:v>projectileSpeed</x:v>
       </x:c>
       <x:c r="E67" t="n">
-        <x:v>4</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="F67"/>
       <x:c r="G67"/>
@@ -5736,7 +5736,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6dc16630ebf47ab"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1665e7083b7a4e47"/>
 </x:worksheet>
 </file>
 
@@ -6014,7 +6014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63bee14851046bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7c92bec775a4aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/excelCfg/roguelike.xlsx
+++ b/excelCfg/roguelike.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R986484eff25b4f9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="R8b49c1bf6f874a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="Rc6ccb3f1c17b4b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R946b5fed626240ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" r:id="R60902f437c4c43ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effects" sheetId="2" r:id="R2265e8b162944b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_runtime" sheetId="3" r:id="R3bfba6595a28449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="4" r:id="R8aa94a8ff5c648b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2030,7 +2030,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f70bdf567e24619"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f783aed25034deb"/>
 </x:worksheet>
 </file>
 
@@ -3066,7 +3066,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>R_E_W_AREA</x:v>
+        <x:v>R_E_W_TORNADO</x:v>
       </x:c>
       <x:c r="B22" t="str">
         <x:v>Skill</x:v>
@@ -3078,28 +3078,28 @@
         <x:v>A0E2</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>冰封扩散</x:v>
+        <x:v>极寒分裂</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>凛风冲击范围增加 {value}。</x:v>
+        <x:v>以中心冰龙卷为基点，额外生成 {value} 个冰龙卷。</x:v>
       </x:c>
       <x:c r="G22" t="str">
         <x:v>ui\selectHero\skills\a0e2.blp</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>area_add</x:v>
+        <x:v>extra_tornado_count_add</x:v>
       </x:c>
       <x:c r="I22" t="str">
         <x:v>add</x:v>
       </x:c>
       <x:c r="J22" t="n">
-        <x:v>60</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K22" t="n">
-        <x:v>110</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L22" t="n">
-        <x:v>180</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M22" t="n">
         <x:v>3</x:v>
@@ -3115,7 +3115,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>R_E_W_DURATION</x:v>
+        <x:v>R_E_W_BOLT</x:v>
       </x:c>
       <x:c r="B23" t="str">
         <x:v>Skill</x:v>
@@ -3127,28 +3127,28 @@
         <x:v>A0E2</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>寒潮延续</x:v>
+        <x:v>凛冬爆裂</x:v>
       </x:c>
       <x:c r="F23" t="str">
-        <x:v>凛风冲击的定身或减速延长 {value_hundredth} 秒。</x:v>
+        <x:v>每个冰龙卷结束时向四周发射 {value} 枚冰箭。</x:v>
       </x:c>
       <x:c r="G23" t="str">
         <x:v>ui\selectHero\skills\a0e2.blp</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>control_duration_hundredths_add</x:v>
+        <x:v>expiry_bolt_count_add</x:v>
       </x:c>
       <x:c r="I23" t="str">
         <x:v>add</x:v>
       </x:c>
       <x:c r="J23" t="n">
-        <x:v>25</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K23" t="n">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L23" t="n">
-        <x:v>75</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M23" t="n">
         <x:v>3</x:v>
@@ -3763,7 +3763,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ccc3818574445f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dd9580240934895"/>
 </x:worksheet>
 </file>
 
@@ -4671,7 +4671,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
-        <x:v>ARTHAS_A0E2_DAMAGE_MULTIPLIER</x:v>
+        <x:v>ARTHAS_A0E2_TICK_DAMAGE_MULTIPLIER</x:v>
       </x:c>
       <x:c r="B44" t="str">
         <x:v>H0E0</x:v>
@@ -4680,17 +4680,17 @@
         <x:v>A0E2</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>damageMultiplierTenth</x:v>
+        <x:v>tickDamageMultiplierHundredth</x:v>
       </x:c>
       <x:c r="E44"/>
       <x:c r="F44" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H44" t="n">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I44"/>
     </x:row>
@@ -5734,9 +5734,177 @@
       <x:c r="H92"/>
       <x:c r="I92"/>
     </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>ARTHAS_A0E2_DURATION</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>durationHundredths</x:v>
+      </x:c>
+      <x:c r="E93" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>ARTHAS_A0E2_TICK_INTERVAL</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>tickIntervalHundredths</x:v>
+      </x:c>
+      <x:c r="E94" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F94"/>
+      <x:c r="G94"/>
+      <x:c r="H94"/>
+      <x:c r="I94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>ARTHAS_A0E2_EXTRA_TORNADO_RING</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>extraTornadoRingRadius</x:v>
+      </x:c>
+      <x:c r="E95" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F95"/>
+      <x:c r="G95"/>
+      <x:c r="H95"/>
+      <x:c r="I95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>ARTHAS_A0E2_BOLT_RANGE</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>boltRange</x:v>
+      </x:c>
+      <x:c r="E96" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="F96"/>
+      <x:c r="G96"/>
+      <x:c r="H96"/>
+      <x:c r="I96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>ARTHAS_A0E2_BOLT_SPEED</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>boltSpeed</x:v>
+      </x:c>
+      <x:c r="E97" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="F97"/>
+      <x:c r="G97"/>
+      <x:c r="H97"/>
+      <x:c r="I97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>ARTHAS_A0E2_BOLT_COLLISION</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>boltCollisionRadius</x:v>
+      </x:c>
+      <x:c r="E98" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>ARTHAS_A0E2_BOLT_DAMAGE_ATTRIBUTE</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>boltDamageAttribute</x:v>
+      </x:c>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+      <x:c r="I99" t="str">
+        <x:v>primary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>ARTHAS_A0E2_BOLT_DAMAGE_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>H0E0</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>A0E2</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>boltDamageMultiplierTenth</x:v>
+      </x:c>
+      <x:c r="E100" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
+      <x:c r="I100"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1665e7083b7a4e47"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree4170e20e2f4921"/>
 </x:worksheet>
 </file>
 
@@ -6014,7 +6182,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7c92bec775a4aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R107859d58ba4477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>